--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>300 000 € 2 608,70 €/m² SURFACE À VENDRE 25 RUE DU MOULIN JOLY 115 m² Belleville-Saint Maur, Paris 11ème arrondissement (75011) Voir l'annonce</t>
+          <t>EVOLIS vous propose à la vente un local d'activité en sous-sol, d'une superficie de 115 m², situé au coeur du 11ème arrondissement dans un quartier vivant et bien desservi. Surface rectangulaire saine sans perte d'espace, avec une bonne hauteur sous plafond et bien équipée. Idéal activités e-commerce, stockage préparation de commandes, artisanat, création, showroom. Disponibilité : immédiate. . Accès livraison . Monte-charge de 800 kg . WC . Kitchenette . VMC Situation/Transports : Bus Ramponeau (20, 71), Couronnes (96, N23, N12) Métro Belleville (11), Couronnes (2) Transilien Gare de l'Est (TER)</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 566 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 503 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.049</v>
+        <v>0.0534</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -937,7 +937,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 503 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +1 122 €/mois.</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>3793.08</v>
+        <v>3354.17</v>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>

--- a/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
+++ b/docs/dossiers/dossier-paris-11eme-arrondissement-48e999a7.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>loyer_estime · rendement_anormalement_eleve</t>
+          <t>loyer_estime · rendement_anormalement_eleve · surface_a_ventiler · occupation_a_confirmer</t>
         </is>
       </c>
     </row>
